--- a/tools/excel_export/excel/bag_items.xlsx
+++ b/tools/excel_export/excel/bag_items.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="85">
   <si>
     <t>id</t>
   </si>
@@ -257,6 +257,15 @@
   </si>
   <si>
     <t>relic_start_gift</t>
+  </si>
+  <si>
+    <t>boost_run_start_kill_points</t>
+  </si>
+  <si>
+    <t>初始击杀券</t>
+  </si>
+  <si>
+    <t>run_start_kill_points</t>
   </si>
 </sst>
 </file>
@@ -696,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -1413,13 +1422,57 @@
         <v>200</v>
       </c>
     </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>1021</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H17" s="4">
+        <v>99</v>
+      </c>
+      <c r="I17" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" s="4">
+        <v>0</v>
+      </c>
+      <c r="L17" s="4">
+        <v>0</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="N17" s="4">
+        <v>210</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="取值非法" error="只能是：common / rare / epic / legendary" sqref="G4:G160">
       <formula1>"common,rare,epic,legendary"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="取值非法" error="只能是：run_start_gold / shop_option_plus / shop_draw_discount / ad_free_draw / kill_buff_discount / gold_gain_bonus / battle_exp_bonus / hero_start_level / hero_select_free / relic_start_gift" sqref="M4:M160">
-      <formula1>"run_start_gold,shop_option_plus,shop_draw_discount,ad_free_draw,kill_buff_discount,gold_gain_bonus,battle_exp_bonus,hero_start_level,hero_select_free,relic_start_gift"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="取值非法" error="只能是：run_start_gold / run_start_kill_points / shop_option_plus / shop_draw_discount / ad_free_draw / kill_buff_discount / gold_gain_bonus / battle_exp_bonus / hero_start_level / hero_select_free / relic_start_gift" sqref="M4:M160">
+      <formula1>"run_start_gold,run_start_kill_points,shop_option_plus,shop_draw_discount,ad_free_draw,kill_buff_discount,gold_gain_bonus,battle_exp_bonus,hero_start_level,hero_select_free,relic_start_gift"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
